--- a/app/src/main/res/raw/pregnancy_visit_form.xlsx
+++ b/app/src/main/res/raw/pregnancy_visit_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27795" windowHeight="12195" tabRatio="500"/>
+    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -1435,7 +1435,7 @@
     <t>repeat_name</t>
   </si>
   <si>
-    <t>xml_node_name</t>
+    <t>repeat_xml_node</t>
   </si>
   <si>
     <t>rawPregnancyVisit</t>
@@ -1461,10 +1461,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1505,6 +1505,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -1513,16 +1520,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1535,16 +1572,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -1561,15 +1598,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1590,23 +1619,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1619,24 +1634,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1705,19 +1705,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1735,13 +1735,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1753,25 +1789,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1783,55 +1801,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1849,19 +1819,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1874,18 +1886,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1988,21 +1988,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -2042,26 +2027,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2076,151 +2041,186 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/app/src/main/res/raw/pregnancy_visit_form.xlsx
+++ b/app/src/main/res/raw/pregnancy_visit_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500" activeTab="2"/>
+    <workbookView windowWidth="22770" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="467">
   <si>
     <t>group</t>
   </si>
@@ -527,9 +527,6 @@
   </si>
   <si>
     <t>start repeat</t>
-  </si>
-  <si>
-    <t>$child_outcomes</t>
   </si>
   <si>
     <t>7. Child's Outcomes</t>
@@ -1461,10 +1458,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1506,22 +1503,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1529,29 +1511,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1559,7 +1527,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1581,6 +1549,51 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="Arial"/>
@@ -1588,17 +1601,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1613,37 +1624,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Arial"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1705,7 +1702,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1717,13 +1732,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1741,19 +1762,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1765,7 +1780,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1777,91 +1792,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1879,13 +1816,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1982,8 +1979,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1992,7 +2019,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2027,17 +2054,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2052,175 +2073,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3627,20 +3624,18 @@
         <v>158</v>
       </c>
       <c r="F26" s="72"/>
-      <c r="G26" s="72" t="s">
+      <c r="G26" s="72"/>
+      <c r="H26" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="59" t="s">
+      <c r="I26" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="I26" s="59" t="s">
+      <c r="J26" s="91" t="s">
         <v>161</v>
       </c>
-      <c r="J26" s="91" t="s">
+      <c r="K26" s="92" t="s">
         <v>162</v>
-      </c>
-      <c r="K26" s="92" t="s">
-        <v>163</v>
       </c>
       <c r="L26" s="93"/>
       <c r="M26" s="93"/>
@@ -3656,25 +3651,25 @@
     <row r="27" spans="1:16">
       <c r="A27" s="1"/>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="H27" t="s">
         <v>165</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>166</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="77" t="s">
         <v>168</v>
-      </c>
-      <c r="K27" s="77" t="s">
-        <v>169</v>
       </c>
       <c r="L27" s="78"/>
       <c r="M27" s="78"/>
@@ -3691,22 +3686,22 @@
     <row r="28" spans="1:16">
       <c r="A28" s="1"/>
       <c r="D28" s="60" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
       </c>
       <c r="H28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" t="s">
         <v>171</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="77" t="s">
         <v>173</v>
-      </c>
-      <c r="K28" s="77" t="s">
-        <v>174</v>
       </c>
       <c r="L28" s="78"/>
       <c r="M28" s="78"/>
@@ -3723,22 +3718,22 @@
     <row r="29" spans="1:16">
       <c r="A29" s="1"/>
       <c r="D29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
       </c>
       <c r="H29" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" t="s">
         <v>176</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="77" t="s">
         <v>178</v>
-      </c>
-      <c r="K29" s="77" t="s">
-        <v>179</v>
       </c>
       <c r="L29" s="78"/>
       <c r="M29" s="78"/>
@@ -3755,25 +3750,25 @@
     <row r="30" spans="1:16">
       <c r="A30" s="1"/>
       <c r="D30" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" t="s">
         <v>181</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>182</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="77" t="s">
         <v>184</v>
-      </c>
-      <c r="K30" s="77" t="s">
-        <v>185</v>
       </c>
       <c r="L30" s="78"/>
       <c r="M30" s="78"/>
@@ -3790,25 +3785,25 @@
     <row r="31" spans="1:16">
       <c r="A31" s="1"/>
       <c r="D31" s="61" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="73" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31" t="s">
         <v>187</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>188</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="77" t="s">
         <v>190</v>
-      </c>
-      <c r="K31" s="77" t="s">
-        <v>191</v>
       </c>
       <c r="L31" s="78"/>
       <c r="M31" s="78"/>
@@ -3822,22 +3817,22 @@
     <row r="32" spans="1:16">
       <c r="A32" s="1"/>
       <c r="D32" s="61" t="s">
+        <v>191</v>
+      </c>
+      <c r="E32" t="s">
         <v>192</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>193</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>194</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="77" t="s">
         <v>196</v>
-      </c>
-      <c r="K32" s="77" t="s">
-        <v>197</v>
       </c>
       <c r="L32" s="78"/>
       <c r="M32" s="78"/>
@@ -3845,13 +3840,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1"/>
       <c r="D33" s="61" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -3860,16 +3855,16 @@
         <v>73</v>
       </c>
       <c r="H33" t="s">
+        <v>199</v>
+      </c>
+      <c r="I33" t="s">
         <v>200</v>
       </c>
-      <c r="I33" t="s">
+      <c r="J33" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="77" t="s">
         <v>202</v>
-      </c>
-      <c r="K33" s="77" t="s">
-        <v>203</v>
       </c>
       <c r="L33" s="78"/>
       <c r="M33" s="78"/>
@@ -3877,31 +3872,31 @@
         <v>1</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1"/>
       <c r="D34" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="E34" t="s">
         <v>205</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="49" t="s">
+      <c r="H34" t="s">
         <v>207</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>208</v>
       </c>
-      <c r="I34" t="s">
+      <c r="J34" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="77" t="s">
         <v>210</v>
-      </c>
-      <c r="K34" s="77" t="s">
-        <v>211</v>
       </c>
       <c r="L34" s="78"/>
       <c r="M34" s="78"/>
@@ -3909,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1"/>
       <c r="D35" s="61" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E35" t="s">
         <v>26</v>
@@ -3924,16 +3919,16 @@
         <v>137</v>
       </c>
       <c r="H35" t="s">
+        <v>213</v>
+      </c>
+      <c r="I35" t="s">
         <v>214</v>
       </c>
-      <c r="I35" t="s">
+      <c r="J35" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="77" t="s">
         <v>216</v>
-      </c>
-      <c r="K35" s="77" t="s">
-        <v>217</v>
       </c>
       <c r="L35" s="78"/>
       <c r="M35" s="78"/>
@@ -3941,31 +3936,31 @@
         <v>1</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1"/>
       <c r="D36" s="61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E36" t="s">
         <v>26</v>
       </c>
       <c r="F36" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" t="s">
         <v>219</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>220</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="77" t="s">
         <v>222</v>
-      </c>
-      <c r="K36" s="77" t="s">
-        <v>223</v>
       </c>
       <c r="L36" s="78"/>
       <c r="M36" s="78"/>
@@ -3973,13 +3968,13 @@
         <v>1</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:16">
       <c r="A37" s="1"/>
       <c r="D37" s="61" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -3989,16 +3984,16 @@
       </c>
       <c r="G37" s="49"/>
       <c r="H37" t="s">
+        <v>224</v>
+      </c>
+      <c r="I37" t="s">
         <v>225</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="77" t="s">
         <v>227</v>
-      </c>
-      <c r="K37" s="77" t="s">
-        <v>228</v>
       </c>
       <c r="L37" s="78"/>
       <c r="M37" s="78"/>
@@ -4012,7 +4007,7 @@
     <row r="38" customFormat="1" spans="1:16">
       <c r="A38" s="1"/>
       <c r="D38" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -4020,16 +4015,16 @@
       <c r="F38" s="49"/>
       <c r="G38" s="49"/>
       <c r="H38" t="s">
+        <v>229</v>
+      </c>
+      <c r="I38" t="s">
         <v>230</v>
       </c>
-      <c r="I38" t="s">
+      <c r="J38" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" s="77" t="s">
         <v>232</v>
-      </c>
-      <c r="K38" s="77" t="s">
-        <v>233</v>
       </c>
       <c r="L38" s="78"/>
       <c r="M38" s="78"/>
@@ -4037,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" s="48" customFormat="1" spans="1:17">
@@ -4048,7 +4043,7 @@
         <v>157</v>
       </c>
       <c r="E39" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F39" s="72"/>
       <c r="G39" s="72"/>
@@ -4065,29 +4060,29 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="62" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B40" s="63"/>
       <c r="C40" s="63"/>
       <c r="D40" s="63" t="s">
+        <v>236</v>
+      </c>
+      <c r="E40" s="63" t="s">
         <v>237</v>
-      </c>
-      <c r="E40" s="63" t="s">
-        <v>238</v>
       </c>
       <c r="F40" s="74"/>
       <c r="G40" s="74"/>
       <c r="H40" s="63" t="s">
+        <v>238</v>
+      </c>
+      <c r="I40" s="63" t="s">
         <v>239</v>
       </c>
-      <c r="I40" s="63" t="s">
+      <c r="J40" s="88" t="s">
         <v>240</v>
       </c>
-      <c r="J40" s="88" t="s">
+      <c r="K40" s="94" t="s">
         <v>241</v>
-      </c>
-      <c r="K40" s="94" t="s">
-        <v>242</v>
       </c>
       <c r="L40" s="95"/>
       <c r="M40" s="95"/>
@@ -4103,29 +4098,29 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B41" s="57"/>
       <c r="C41" s="57"/>
       <c r="D41" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="E41" s="57" t="s">
         <v>243</v>
-      </c>
-      <c r="E41" s="57" t="s">
-        <v>244</v>
       </c>
       <c r="F41" s="71"/>
       <c r="G41" s="71"/>
       <c r="H41" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="I41" s="57" t="s">
         <v>245</v>
       </c>
-      <c r="I41" s="57" t="s">
+      <c r="J41" s="88" t="s">
         <v>246</v>
       </c>
-      <c r="J41" s="88" t="s">
+      <c r="K41" s="89" t="s">
         <v>247</v>
-      </c>
-      <c r="K41" s="89" t="s">
-        <v>248</v>
       </c>
       <c r="L41" s="90"/>
       <c r="M41" s="90"/>
@@ -4141,29 +4136,29 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B42" s="57"/>
       <c r="C42" s="57"/>
       <c r="D42" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="E42" s="57" t="s">
         <v>249</v>
-      </c>
-      <c r="E42" s="57" t="s">
-        <v>250</v>
       </c>
       <c r="F42" s="57"/>
       <c r="G42" s="57"/>
       <c r="H42" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="I42" s="57" t="s">
+        <v>250</v>
+      </c>
+      <c r="J42" s="88" t="s">
+        <v>250</v>
+      </c>
+      <c r="K42" s="89" t="s">
         <v>251</v>
-      </c>
-      <c r="I42" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="J42" s="88" t="s">
-        <v>251</v>
-      </c>
-      <c r="K42" s="89" t="s">
-        <v>252</v>
       </c>
       <c r="L42" s="90"/>
       <c r="M42" s="90"/>
@@ -4179,12 +4174,12 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B43" s="57"/>
       <c r="C43" s="57"/>
       <c r="D43" s="57" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E43" s="57" t="s">
         <v>20</v>
@@ -4192,16 +4187,16 @@
       <c r="F43" s="57"/>
       <c r="G43" s="57"/>
       <c r="H43" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="I43" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="88" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" s="89" t="s">
         <v>254</v>
-      </c>
-      <c r="I43" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="J43" s="88" t="s">
-        <v>254</v>
-      </c>
-      <c r="K43" s="89" t="s">
-        <v>255</v>
       </c>
       <c r="L43" s="90"/>
       <c r="M43" s="90"/>
@@ -4217,12 +4212,12 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="64" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B44" s="57"/>
       <c r="C44" s="57"/>
       <c r="D44" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>20</v>
@@ -4230,16 +4225,16 @@
       <c r="F44" s="57"/>
       <c r="G44" s="57"/>
       <c r="H44" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="I44" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="J44" s="88" t="s">
+        <v>256</v>
+      </c>
+      <c r="K44" s="89" t="s">
         <v>257</v>
-      </c>
-      <c r="I44" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="J44" s="88" t="s">
-        <v>257</v>
-      </c>
-      <c r="K44" s="89" t="s">
-        <v>258</v>
       </c>
       <c r="L44" s="90"/>
       <c r="M44" s="90"/>
@@ -4255,12 +4250,12 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="65" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B45" s="66"/>
       <c r="C45" s="66"/>
       <c r="D45" s="66" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E45" s="66" t="s">
         <v>20</v>
@@ -4268,16 +4263,16 @@
       <c r="F45" s="75"/>
       <c r="G45" s="75"/>
       <c r="H45" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="I45" s="66" t="s">
         <v>260</v>
       </c>
-      <c r="I45" s="66" t="s">
+      <c r="J45" s="88" t="s">
         <v>261</v>
       </c>
-      <c r="J45" s="88" t="s">
+      <c r="K45" s="94" t="s">
         <v>262</v>
-      </c>
-      <c r="K45" s="94" t="s">
-        <v>263</v>
       </c>
       <c r="L45" s="96"/>
       <c r="M45" s="96"/>
@@ -4376,7 +4371,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>7</v>
@@ -4408,19 +4403,19 @@
         <v>73</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="F2" s="31" t="s">
         <v>268</v>
-      </c>
-      <c r="F2" s="31" t="s">
-        <v>269</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
@@ -4432,19 +4427,19 @@
         <v>73</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="F3" s="31" t="s">
         <v>273</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>274</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
@@ -4453,22 +4448,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="F4" s="33" t="s">
         <v>278</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>279</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="7"/>
@@ -4477,22 +4472,22 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="F5" s="33" t="s">
         <v>283</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>284</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="7"/>
@@ -4501,26 +4496,26 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="34" t="s">
         <v>287</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="F6" s="35" t="s">
         <v>288</v>
-      </c>
-      <c r="F6" s="35" t="s">
-        <v>289</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="36" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -4530,19 +4525,19 @@
         <v>27</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="F7" s="38" t="s">
         <v>294</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>295</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="23"/>
@@ -4554,19 +4549,19 @@
         <v>27</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="E8" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="F8" s="38" t="s">
         <v>299</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>300</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="23"/>
@@ -4578,19 +4573,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="E9" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="F9" s="39" t="s">
         <v>304</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>305</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -4602,19 +4597,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="D10" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="E10" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="F10" s="39" t="s">
         <v>309</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>310</v>
       </c>
       <c r="G10" s="16" t="b">
         <v>1</v>
@@ -4628,19 +4623,19 @@
         <v>61</v>
       </c>
       <c r="B11" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="D11" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="E11" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="F11" s="39" t="s">
         <v>314</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>315</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
@@ -4649,22 +4644,22 @@
     </row>
     <row r="12" s="4" customFormat="1" spans="1:10">
       <c r="A12" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="E12" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="F12" s="38" t="s">
         <v>319</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>320</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="23"/>
@@ -4673,22 +4668,22 @@
     </row>
     <row r="13" s="4" customFormat="1" spans="1:10">
       <c r="A13" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="E13" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="F13" s="40" t="s">
         <v>324</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>325</v>
       </c>
       <c r="G13" s="4" t="b">
         <v>1</v>
@@ -4699,22 +4694,22 @@
     </row>
     <row r="14" s="4" customFormat="1" spans="1:10">
       <c r="A14" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B14" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="E14" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="F14" s="40" t="s">
         <v>329</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>330</v>
       </c>
       <c r="G14" s="4" t="b">
         <v>1</v>
@@ -4725,22 +4720,22 @@
     </row>
     <row r="15" s="4" customFormat="1" spans="1:10">
       <c r="A15" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="E15" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="F15" s="40" t="s">
         <v>334</v>
-      </c>
-      <c r="F15" s="40" t="s">
-        <v>335</v>
       </c>
       <c r="G15" s="4" t="b">
         <v>1</v>
@@ -4751,22 +4746,22 @@
     </row>
     <row r="16" s="4" customFormat="1" spans="1:10">
       <c r="A16" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="E16" s="37" t="s">
         <v>338</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="F16" s="38" t="s">
         <v>339</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>340</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="23"/>
@@ -4775,22 +4770,22 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B17" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="C17" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="D17" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="30" t="s">
         <v>343</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="F17" s="31" t="s">
         <v>344</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>345</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -4799,22 +4794,22 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="E18" s="30" t="s">
-        <v>348</v>
-      </c>
       <c r="F18" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -4823,22 +4818,22 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B19" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="D19" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="F19" s="31" t="s">
         <v>329</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>330</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -4847,22 +4842,22 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B20" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="D20" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="F20" s="31" t="s">
         <v>334</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>335</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -4874,19 +4869,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="D21" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="E21" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="F21" s="42" t="s">
         <v>352</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>353</v>
       </c>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
@@ -4898,19 +4893,19 @@
         <v>102</v>
       </c>
       <c r="B22" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="C22" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="D22" s="23" t="s">
         <v>355</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="E22" s="41" t="s">
         <v>356</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="F22" s="42" t="s">
         <v>357</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>358</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
@@ -4922,19 +4917,19 @@
         <v>102</v>
       </c>
       <c r="B23" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="C23" s="22" t="s">
         <v>359</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="D23" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="D23" s="23" t="s">
+      <c r="E23" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="F23" s="42" t="s">
         <v>362</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>363</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -4946,19 +4941,19 @@
         <v>102</v>
       </c>
       <c r="B24" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="22" t="s">
         <v>364</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="D24" s="23" t="s">
         <v>365</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="E24" s="41" t="s">
         <v>366</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="F24" s="42" t="s">
         <v>367</v>
-      </c>
-      <c r="F24" s="42" t="s">
-        <v>368</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
@@ -4970,19 +4965,19 @@
         <v>102</v>
       </c>
       <c r="B25" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="22" t="s">
         <v>369</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="D25" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="E25" s="41" t="s">
         <v>371</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="F25" s="42" t="s">
         <v>372</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>373</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
@@ -4994,19 +4989,19 @@
         <v>102</v>
       </c>
       <c r="B26" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="D26" s="23" t="s">
         <v>375</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="E26" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="E26" s="41" t="s">
+      <c r="F26" s="42" t="s">
         <v>377</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>378</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
@@ -5018,19 +5013,19 @@
         <v>102</v>
       </c>
       <c r="B27" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>379</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="D27" s="23" t="s">
         <v>380</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="E27" s="41" t="s">
         <v>381</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="F27" s="42" t="s">
         <v>382</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>383</v>
       </c>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
@@ -5042,19 +5037,19 @@
         <v>79</v>
       </c>
       <c r="B28" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="D28" s="25" t="s">
         <v>350</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="E28" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="F28" s="43" t="s">
         <v>352</v>
-      </c>
-      <c r="F28" s="43" t="s">
-        <v>353</v>
       </c>
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
@@ -5066,19 +5061,19 @@
         <v>79</v>
       </c>
       <c r="B29" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="D29" s="25" t="s">
         <v>355</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="E29" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="F29" s="43" t="s">
         <v>357</v>
-      </c>
-      <c r="F29" s="43" t="s">
-        <v>358</v>
       </c>
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
@@ -5090,19 +5085,19 @@
         <v>79</v>
       </c>
       <c r="B30" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C30" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="D30" s="25" t="s">
         <v>360</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="E30" s="25" t="s">
         <v>361</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="F30" s="43" t="s">
         <v>362</v>
-      </c>
-      <c r="F30" s="43" t="s">
-        <v>363</v>
       </c>
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
@@ -5114,19 +5109,19 @@
         <v>79</v>
       </c>
       <c r="B31" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C31" s="25" t="s">
         <v>364</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="D31" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="E31" s="25" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="F31" s="43" t="s">
         <v>367</v>
-      </c>
-      <c r="F31" s="43" t="s">
-        <v>368</v>
       </c>
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
@@ -5138,19 +5133,19 @@
         <v>79</v>
       </c>
       <c r="B32" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>369</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="D32" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="E32" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="F32" s="43" t="s">
         <v>372</v>
-      </c>
-      <c r="F32" s="43" t="s">
-        <v>373</v>
       </c>
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
@@ -5162,19 +5157,19 @@
         <v>79</v>
       </c>
       <c r="B33" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>374</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="D33" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="E33" s="25" t="s">
         <v>376</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="F33" s="43" t="s">
         <v>377</v>
-      </c>
-      <c r="F33" s="43" t="s">
-        <v>378</v>
       </c>
       <c r="G33" s="25"/>
       <c r="H33" s="25"/>
@@ -5186,19 +5181,19 @@
         <v>79</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="D34" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="D34" s="25" t="s">
+      <c r="E34" s="25" t="s">
         <v>381</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="F34" s="43" t="s">
         <v>382</v>
-      </c>
-      <c r="F34" s="43" t="s">
-        <v>383</v>
       </c>
       <c r="G34" s="25"/>
       <c r="H34" s="25"/>
@@ -5210,19 +5205,19 @@
         <v>137</v>
       </c>
       <c r="B35" s="17" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>384</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="D35" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="E35" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="F35" s="39" t="s">
         <v>387</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>388</v>
       </c>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
@@ -5234,19 +5229,19 @@
         <v>137</v>
       </c>
       <c r="B36" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="E36" s="16" t="s">
         <v>391</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="F36" s="39" t="s">
         <v>392</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>393</v>
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
@@ -5258,19 +5253,19 @@
         <v>137</v>
       </c>
       <c r="B37" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>394</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>395</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="E37" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="F37" s="39" t="s">
         <v>397</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>398</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
@@ -5279,246 +5274,246 @@
     </row>
     <row r="38" s="4" customFormat="1" spans="1:7">
       <c r="A38" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" s="27" t="s">
+        <v>398</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="D38" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="F38" s="44" t="s">
         <v>402</v>
-      </c>
-      <c r="F38" s="44" t="s">
-        <v>403</v>
       </c>
       <c r="G38" s="22"/>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:7">
       <c r="A39" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B39" s="27" t="s">
+        <v>403</v>
+      </c>
+      <c r="C39" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="D39" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="F39" s="44" t="s">
         <v>407</v>
-      </c>
-      <c r="F39" s="44" t="s">
-        <v>408</v>
       </c>
       <c r="G39" s="22"/>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:7">
       <c r="A40" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B40" s="27" t="s">
+        <v>408</v>
+      </c>
+      <c r="C40" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="D40" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="F40" s="44" t="s">
         <v>412</v>
-      </c>
-      <c r="F40" s="44" t="s">
-        <v>413</v>
       </c>
       <c r="G40" s="22"/>
     </row>
     <row r="41" s="4" customFormat="1" spans="1:7">
       <c r="A41" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C41" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="F41" s="44" t="s">
         <v>288</v>
-      </c>
-      <c r="F41" s="44" t="s">
-        <v>289</v>
       </c>
       <c r="G41" s="22"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>415</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="D42" t="s">
         <v>416</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>417</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B43" s="29" t="s">
+        <v>419</v>
+      </c>
+      <c r="C43" s="28" t="s">
         <v>420</v>
       </c>
-      <c r="C43" s="28" t="s">
+      <c r="D43" t="s">
         <v>421</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>422</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B44" s="29" t="s">
+        <v>424</v>
+      </c>
+      <c r="C44" s="28" t="s">
         <v>425</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="D44" t="s">
         <v>426</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>427</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B45" s="29" t="s">
+        <v>429</v>
+      </c>
+      <c r="C45" s="28" t="s">
         <v>430</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="D45" t="s">
         <v>431</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>432</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" s="29" t="s">
+        <v>434</v>
+      </c>
+      <c r="C46" s="28" t="s">
         <v>435</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="D46" t="s">
         <v>436</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>437</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B47" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="C47" s="28" t="s">
         <v>440</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="D47" t="s">
         <v>441</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>442</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="C48" s="28" t="s">
         <v>445</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="D48" t="s">
         <v>446</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>447</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B49" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="D49" t="s">
         <v>450</v>
       </c>
-      <c r="C49" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>451</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="51" spans="4:9">
@@ -5609,45 +5604,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>455</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>457</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>458</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B2" t="s">
         <v>462</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>463</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -5656,7 +5651,7 @@
         <v>157</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/app/src/main/res/raw/pregnancy_visit_form.xlsx
+++ b/app/src/main/res/raw/pregnancy_visit_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22770" windowHeight="12315" tabRatio="500"/>
+    <workbookView windowWidth="27795" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="468">
   <si>
     <t>group</t>
   </si>
@@ -527,6 +527,9 @@
   </si>
   <si>
     <t>start repeat</t>
+  </si>
+  <si>
+    <t>$external</t>
   </si>
   <si>
     <t>7. Child's Outcomes</t>
@@ -1458,10 +1461,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -1502,8 +1505,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1525,14 +1529,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1540,11 +1536,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1557,14 +1568,60 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1579,30 +1636,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1610,37 +1644,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1708,7 +1711,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1720,13 +1747,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1744,55 +1867,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1804,85 +1885,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1976,15 +1979,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1996,6 +1990,45 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2017,39 +2050,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2065,159 +2070,157 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3624,18 +3627,20 @@
         <v>158</v>
       </c>
       <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
+      <c r="G26" s="72" t="s">
+        <v>159</v>
+      </c>
       <c r="H26" s="59" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I26" s="59" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J26" s="91" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K26" s="92" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L26" s="93"/>
       <c r="M26" s="93"/>
@@ -3651,25 +3656,25 @@
     <row r="27" spans="1:16">
       <c r="A27" s="1"/>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K27" s="77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L27" s="78"/>
       <c r="M27" s="78"/>
@@ -3686,22 +3691,22 @@
     <row r="28" spans="1:16">
       <c r="A28" s="1"/>
       <c r="D28" s="60" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K28" s="77" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L28" s="78"/>
       <c r="M28" s="78"/>
@@ -3718,22 +3723,22 @@
     <row r="29" spans="1:16">
       <c r="A29" s="1"/>
       <c r="D29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K29" s="77" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L29" s="78"/>
       <c r="M29" s="78"/>
@@ -3750,25 +3755,25 @@
     <row r="30" spans="1:16">
       <c r="A30" s="1"/>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H30" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I30" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K30" s="77" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L30" s="78"/>
       <c r="M30" s="78"/>
@@ -3785,25 +3790,25 @@
     <row r="31" spans="1:16">
       <c r="A31" s="1"/>
       <c r="D31" s="61" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
       </c>
       <c r="F31" s="73" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I31" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K31" s="77" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L31" s="78"/>
       <c r="M31" s="78"/>
@@ -3817,22 +3822,22 @@
     <row r="32" spans="1:16">
       <c r="A32" s="1"/>
       <c r="D32" s="61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I32" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K32" s="77" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L32" s="78"/>
       <c r="M32" s="78"/>
@@ -3840,13 +3845,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="1"/>
       <c r="D33" s="61" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
@@ -3855,16 +3860,16 @@
         <v>73</v>
       </c>
       <c r="H33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I33" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K33" s="77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L33" s="78"/>
       <c r="M33" s="78"/>
@@ -3872,31 +3877,31 @@
         <v>1</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="1"/>
       <c r="D34" s="61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F34" s="49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H34" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K34" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L34" s="78"/>
       <c r="M34" s="78"/>
@@ -3904,13 +3909,13 @@
         <v>1</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="1"/>
       <c r="D35" s="61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E35" t="s">
         <v>26</v>
@@ -3919,16 +3924,16 @@
         <v>137</v>
       </c>
       <c r="H35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K35" s="77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L35" s="78"/>
       <c r="M35" s="78"/>
@@ -3936,31 +3941,31 @@
         <v>1</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="1"/>
       <c r="D36" s="61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E36" t="s">
         <v>26</v>
       </c>
       <c r="F36" s="49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H36" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I36" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K36" s="77" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L36" s="78"/>
       <c r="M36" s="78"/>
@@ -3968,13 +3973,13 @@
         <v>1</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:16">
       <c r="A37" s="1"/>
       <c r="D37" s="61" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -3984,16 +3989,16 @@
       </c>
       <c r="G37" s="49"/>
       <c r="H37" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I37" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K37" s="77" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L37" s="78"/>
       <c r="M37" s="78"/>
@@ -4007,7 +4012,7 @@
     <row r="38" customFormat="1" spans="1:16">
       <c r="A38" s="1"/>
       <c r="D38" s="61" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -4015,16 +4020,16 @@
       <c r="F38" s="49"/>
       <c r="G38" s="49"/>
       <c r="H38" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I38" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K38" s="77" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L38" s="78"/>
       <c r="M38" s="78"/>
@@ -4032,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" s="48" customFormat="1" spans="1:17">
@@ -4043,7 +4048,7 @@
         <v>157</v>
       </c>
       <c r="E39" s="59" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F39" s="72"/>
       <c r="G39" s="72"/>
@@ -4060,29 +4065,29 @@
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="62" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B40" s="63"/>
       <c r="C40" s="63"/>
       <c r="D40" s="63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E40" s="63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F40" s="74"/>
       <c r="G40" s="74"/>
       <c r="H40" s="63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I40" s="63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J40" s="88" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K40" s="94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L40" s="95"/>
       <c r="M40" s="95"/>
@@ -4098,29 +4103,29 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="64" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B41" s="57"/>
       <c r="C41" s="57"/>
       <c r="D41" s="57" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E41" s="57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F41" s="71"/>
       <c r="G41" s="71"/>
       <c r="H41" s="57" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I41" s="57" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J41" s="88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K41" s="89" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L41" s="90"/>
       <c r="M41" s="90"/>
@@ -4136,29 +4141,29 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="64" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B42" s="57"/>
       <c r="C42" s="57"/>
       <c r="D42" s="57" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E42" s="57" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F42" s="57"/>
       <c r="G42" s="57"/>
       <c r="H42" s="57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I42" s="57" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J42" s="88" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K42" s="89" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L42" s="90"/>
       <c r="M42" s="90"/>
@@ -4174,12 +4179,12 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="64" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B43" s="57"/>
       <c r="C43" s="57"/>
       <c r="D43" s="57" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E43" s="57" t="s">
         <v>20</v>
@@ -4187,16 +4192,16 @@
       <c r="F43" s="57"/>
       <c r="G43" s="57"/>
       <c r="H43" s="57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I43" s="57" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J43" s="88" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K43" s="89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L43" s="90"/>
       <c r="M43" s="90"/>
@@ -4212,12 +4217,12 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="64" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B44" s="57"/>
       <c r="C44" s="57"/>
       <c r="D44" s="57" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E44" s="57" t="s">
         <v>20</v>
@@ -4225,16 +4230,16 @@
       <c r="F44" s="57"/>
       <c r="G44" s="57"/>
       <c r="H44" s="57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I44" s="57" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J44" s="88" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L44" s="90"/>
       <c r="M44" s="90"/>
@@ -4250,12 +4255,12 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B45" s="66"/>
       <c r="C45" s="66"/>
       <c r="D45" s="66" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E45" s="66" t="s">
         <v>20</v>
@@ -4263,16 +4268,16 @@
       <c r="F45" s="75"/>
       <c r="G45" s="75"/>
       <c r="H45" s="66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I45" s="66" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J45" s="88" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K45" s="94" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L45" s="96"/>
       <c r="M45" s="96"/>
@@ -4371,7 +4376,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>7</v>
@@ -4403,19 +4408,19 @@
         <v>73</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="7"/>
@@ -4427,19 +4432,19 @@
         <v>73</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="7"/>
@@ -4448,22 +4453,22 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="7"/>
@@ -4472,22 +4477,22 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="7"/>
@@ -4496,26 +4501,26 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -4525,19 +4530,19 @@
         <v>27</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G7" s="14"/>
       <c r="H7" s="23"/>
@@ -4549,19 +4554,19 @@
         <v>27</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="23"/>
@@ -4573,19 +4578,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F9" s="39" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
@@ -4597,19 +4602,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G10" s="16" t="b">
         <v>1</v>
@@ -4623,19 +4628,19 @@
         <v>61</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16"/>
@@ -4644,22 +4649,22 @@
     </row>
     <row r="12" s="4" customFormat="1" spans="1:10">
       <c r="A12" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="23"/>
@@ -4668,22 +4673,22 @@
     </row>
     <row r="13" s="4" customFormat="1" spans="1:10">
       <c r="A13" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G13" s="4" t="b">
         <v>1</v>
@@ -4694,22 +4699,22 @@
     </row>
     <row r="14" s="4" customFormat="1" spans="1:10">
       <c r="A14" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G14" s="4" t="b">
         <v>1</v>
@@ -4720,22 +4725,22 @@
     </row>
     <row r="15" s="4" customFormat="1" spans="1:10">
       <c r="A15" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F15" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="4" t="b">
         <v>1</v>
@@ -4746,22 +4751,22 @@
     </row>
     <row r="16" s="4" customFormat="1" spans="1:10">
       <c r="A16" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="23"/>
@@ -4770,22 +4775,22 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -4794,22 +4799,22 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
@@ -4818,22 +4823,22 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
@@ -4842,22 +4847,22 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -4869,19 +4874,19 @@
         <v>102</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G21" s="23"/>
       <c r="H21" s="23"/>
@@ -4893,19 +4898,19 @@
         <v>102</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
@@ -4917,19 +4922,19 @@
         <v>102</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G23" s="23"/>
       <c r="H23" s="23"/>
@@ -4941,19 +4946,19 @@
         <v>102</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G24" s="23"/>
       <c r="H24" s="23"/>
@@ -4965,19 +4970,19 @@
         <v>102</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G25" s="23"/>
       <c r="H25" s="23"/>
@@ -4989,19 +4994,19 @@
         <v>102</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G26" s="23"/>
       <c r="H26" s="23"/>
@@ -5013,19 +5018,19 @@
         <v>102</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
@@ -5037,19 +5042,19 @@
         <v>79</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E28" s="25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G28" s="25"/>
       <c r="H28" s="25"/>
@@ -5061,19 +5066,19 @@
         <v>79</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G29" s="25"/>
       <c r="H29" s="25"/>
@@ -5085,19 +5090,19 @@
         <v>79</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F30" s="43" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G30" s="25"/>
       <c r="H30" s="25"/>
@@ -5109,19 +5114,19 @@
         <v>79</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G31" s="25"/>
       <c r="H31" s="25"/>
@@ -5133,19 +5138,19 @@
         <v>79</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G32" s="25"/>
       <c r="H32" s="25"/>
@@ -5157,19 +5162,19 @@
         <v>79</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E33" s="25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G33" s="25"/>
       <c r="H33" s="25"/>
@@ -5181,19 +5186,19 @@
         <v>79</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F34" s="43" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G34" s="25"/>
       <c r="H34" s="25"/>
@@ -5205,19 +5210,19 @@
         <v>137</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
@@ -5229,19 +5234,19 @@
         <v>137</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="16"/>
@@ -5253,19 +5258,19 @@
         <v>137</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F37" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
@@ -5274,246 +5279,246 @@
     </row>
     <row r="38" s="4" customFormat="1" spans="1:7">
       <c r="A38" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G38" s="22"/>
     </row>
     <row r="39" s="4" customFormat="1" spans="1:7">
       <c r="A39" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G39" s="22"/>
     </row>
     <row r="40" s="4" customFormat="1" spans="1:7">
       <c r="A40" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F40" s="44" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G40" s="22"/>
     </row>
     <row r="41" s="4" customFormat="1" spans="1:7">
       <c r="A41" s="26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G41" s="22"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B42" s="29" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D42" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E42" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D43" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E43" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D44" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E44" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D45" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E45" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D46" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E46" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D47" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E47" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D48" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E48" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="28" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D49" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E49" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="51" spans="4:9">
@@ -5604,45 +5609,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -5651,7 +5656,7 @@
         <v>157</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
